--- a/config_medici.xlsx
+++ b/config_medici.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/x238574_one_merckgroup_com/Documents/Desktop/PERSONALI/PEGASO/ELABORATO TESI/REV 10.0 -- RESERV_DONE_NOT DONE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/x238574_one_merckgroup_com/Documents/Desktop/PERSONALI/PEGASO/ELABORATO TESI/Rev.9.0 -- CLEAR_OPTIMIZE_CODE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_F25DC773A252ABDACC1048E6D1DB51785BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{607F1E44-703F-40EA-81DA-8B5F20E58739}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="11_F25DC773A252ABDACC1048E6D1DB51785BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D844984-521D-4463-B994-CEB3920DC182}"/>
   <bookViews>
     <workbookView xWindow="-13296" yWindow="-16380" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
   <si>
     <t>MEDICO</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Visita Geriatrica</t>
   </si>
   <si>
-    <t>Visita Remautologica</t>
-  </si>
-  <si>
     <t>Visita Gastroenterologica</t>
   </si>
   <si>
@@ -110,6 +107,66 @@
   </si>
   <si>
     <t>Visita Dietologica</t>
+  </si>
+  <si>
+    <t>Visita Reumatologica</t>
+  </si>
+  <si>
+    <t>Del Gatto</t>
+  </si>
+  <si>
+    <t>Del Cane</t>
+  </si>
+  <si>
+    <t>Agnello</t>
+  </si>
+  <si>
+    <t>Melone</t>
+  </si>
+  <si>
+    <t>Ciliegia</t>
+  </si>
+  <si>
+    <t>Limone</t>
+  </si>
+  <si>
+    <t>Del Toro</t>
+  </si>
+  <si>
+    <t>Viola</t>
+  </si>
+  <si>
+    <t>Marrone</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Pedone</t>
+  </si>
+  <si>
+    <t>Fante</t>
+  </si>
+  <si>
+    <t>Cavallo</t>
+  </si>
+  <si>
+    <t>Fiore</t>
+  </si>
+  <si>
+    <t>Neri</t>
+  </si>
+  <si>
+    <t>Abete</t>
+  </si>
+  <si>
+    <t>Oliva</t>
+  </si>
+  <si>
+    <t>Prato</t>
+  </si>
+  <si>
+    <t>Giardino</t>
   </si>
 </sst>
 </file>
@@ -168,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -182,6 +239,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -471,6 +531,7 @@
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
     <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.109375" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" customWidth="1"/>
@@ -510,7 +571,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
@@ -518,7 +579,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -526,7 +587,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>13</v>
@@ -534,123 +595,131 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -675,14 +744,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021FBCB8-26FF-42D0-A559-5497D064DC69}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="10.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -743,7 +814,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B5" s="5">
         <v>46186</v>
@@ -757,7 +828,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5">
         <v>46187</v>
@@ -771,7 +842,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5">
         <v>46188</v>
@@ -785,7 +856,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B8" s="5">
         <v>46189</v>
@@ -799,7 +870,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5">
         <v>46190</v>
@@ -813,7 +884,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B10" s="5">
         <v>46191</v>
@@ -827,7 +898,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5">
         <v>46192</v>
@@ -841,7 +912,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5">
         <v>46193</v>
@@ -855,7 +926,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5">
         <v>46194</v>
@@ -869,7 +940,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B14" s="5">
         <v>46195</v>
@@ -883,7 +954,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5">
         <v>46196</v>
@@ -897,7 +968,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5">
         <v>46197</v>
@@ -911,7 +982,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5">
         <v>46198</v>
@@ -925,7 +996,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5">
         <v>46199</v>
@@ -939,7 +1010,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B19" s="5">
         <v>46200</v>
@@ -953,7 +1024,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B20" s="5">
         <v>46201</v>
@@ -967,7 +1038,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5">
         <v>46202</v>
@@ -981,29 +1052,45 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B22" s="5">
-        <v>46203</v>
+        <v>46190</v>
       </c>
       <c r="C22" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D22" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.79166666666666663</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.79166666666666663</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
@@ -1042,22 +1129,16 @@
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
